--- a/business-libraries/test-data/self_growth/output_template.xlsx
+++ b/business-libraries/test-data/self_growth/output_template.xlsx
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL-SG-RED-SUMMARY</v>
+        <v>SELF_GROWTH_TPL_PURPLE_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>self_growth</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>purple</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>评估显示，您在「${维度名1}」和「${维度名2}」两个维度上的得分同时处于高危水平。疲惫与意义感同时告急，需要优先关注。</v>
+        <v>评估显示，您在「${主要归因}」上的信号已经处于需要重点关注的位置。系统已暂停常规建议并生成转介工单，心理专员会与您联系。在此之前，请优先照顾好自己的基本作息。</v>
       </c>
       <c r="F2" t="str">
-        <v>${维度名1} ${维度名2} 会被替换为实际触发红线的维度中文名</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,7 +447,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL-SG-RED-CONCLUSION</v>
+        <v>SELF_GROWTH_TPL_RED_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>self_growth</v>
@@ -456,13 +456,13 @@
         <v>red</v>
       </c>
       <c r="D3" t="str">
-        <v>conclusion</v>
+        <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次评估结论：${主归因}（${次归因}）。已触发安全熔断，常规建议暂停输出。</v>
+        <v>本次评估的主要归因是「${主要归因}」，同时「${次要归因}」也需要一并关注。建议本周内安排一次支持性沟通，并从推荐工具中选一项今天就能开始的动作。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主归因} 来自归因-分级规则.主归因；${次归因} 来自归因-分级规则.次归因</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL-SG-RED-GOAL</v>
+        <v>SELF_GROWTH_TPL_ORANGE_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>self_growth</v>
       </c>
       <c r="C4" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="D4" t="str">
-        <v>goal</v>
+        <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>当前首要目标：1) 确保教师获得即时心理支持 2) 降低当前的急性压力水平 3) 建立至少一个可依赖的支持关系</v>
+        <v>本次评估提示「${主要归因}」已进入需要主动支持的区间。重点不是再增加任务，而是先识别消耗来源、恢复可控感。</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,22 +493,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL-SG-ORANGE-ATTRIBUTION</v>
+        <v>SELF_GROWTH_TPL_YELLOW_SUMMARY</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="D5" t="str">
-        <v>attribution</v>
+        <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次评估的归因分析：${主归因}。建议重点关注以下方面：${工具标签}</v>
+        <v>本次评估提示「${主要归因}」值得关注，尚未到需要外部介入的程度，建议先用推荐工具自主调整。</v>
       </c>
       <c r="F5" t="str">
-        <v>${主归因} ${工具标签} 从归因规则中取值</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G5" t="str">
         <v>4</v>
@@ -516,22 +516,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TPL-SG-ORANGE-ACTION</v>
+        <v>SELF_GROWTH_TPL_BLUE_SUMMARY</v>
       </c>
       <c r="B6" t="str">
         <v>self_growth</v>
       </c>
       <c r="C6" t="str">
-        <v>orange</v>
+        <v>blue</v>
       </c>
       <c r="D6" t="str">
-        <v>action</v>
+        <v>summary</v>
       </c>
       <c r="E6" t="str">
-        <v>根据评估结果，建议采取以下行动：${输出动作摘要}。推荐工具：${输出工具摘要}。</v>
+        <v>本次评估显示存在轻微波动，主要落在「${主要归因}」。保持现有节奏，留意变化即可。</v>
       </c>
       <c r="F6" t="str">
-        <v>${输出动作摘要} ${输出工具摘要} 从归因规则中取值</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G6" t="str">
         <v>5</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TPL-SG-GREEN-SUMMARY</v>
+        <v>SELF_GROWTH_TPL_GREEN_SUMMARY</v>
       </c>
       <c r="B7" t="str">
         <v>self_growth</v>
@@ -551,10 +551,10 @@
         <v>summary</v>
       </c>
       <c r="E7" t="str">
-        <v>本次评估结果整体良好，各项指标均在正常范围内。继续保持现有节奏。</v>
+        <v>本次评估未发现需要重点干预的信号，当前状态整体稳定，保持现有节奏即可。</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G7" t="str">
         <v>6</v>

--- a/business-libraries/test-data/self_growth/output_template.xlsx
+++ b/business-libraries/test-data/self_growth/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SELF_GROWTH_TPL_PURPLE_SUMMARY</v>
+        <v>TPL_SG_RED_1</v>
       </c>
       <c r="B2" t="str">
         <v>self_growth</v>
       </c>
       <c r="C2" t="str">
-        <v>purple</v>
+        <v>red</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
@@ -439,7 +439,7 @@
         <v>评估显示，您在「${主要归因}」上的信号已经处于需要重点关注的位置。系统已暂停常规建议并生成转介工单，心理专员会与您联系。在此之前，请优先照顾好自己的基本作息。</v>
       </c>
       <c r="F2" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SELF_GROWTH_TPL_RED_SUMMARY</v>
+        <v>TPL_SG_ORANGE_2</v>
       </c>
       <c r="B3" t="str">
         <v>self_growth</v>
       </c>
       <c r="C3" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
@@ -462,7 +462,7 @@
         <v>本次评估的主要归因是「${主要归因}」，同时「${次要归因}」也需要一并关注。建议本周内安排一次支持性沟通，并从推荐工具中选一项今天就能开始的动作。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SELF_GROWTH_TPL_ORANGE_SUMMARY</v>
+        <v>TPL_SG_YELLOW_3</v>
       </c>
       <c r="B4" t="str">
         <v>self_growth</v>
       </c>
       <c r="C4" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次评估提示「${主要归因}」已进入需要主动支持的区间。重点不是再增加任务，而是先识别消耗来源、恢复可控感。</v>
+        <v>本次评估提示「${主要归因}」值得关注，尚未到需要外部介入的程度，建议先用推荐工具自主调整。</v>
       </c>
       <c r="F4" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,76 +493,30 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SELF_GROWTH_TPL_YELLOW_SUMMARY</v>
+        <v>TPL_SG_DEFAULT</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>yellow</v>
+        <v>green</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次评估提示「${主要归因}」值得关注，尚未到需要外部介入的程度，建议先用推荐工具自主调整。</v>
+        <v>本次评估未发现需要重点干预的信号，当前状态整体稳定，保持现有节奏即可。</v>
       </c>
       <c r="F5" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>兜底模板：命中未覆盖等级时使用</v>
       </c>
       <c r="G5" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>SELF_GROWTH_TPL_BLUE_SUMMARY</v>
-      </c>
-      <c r="B6" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C6" t="str">
-        <v>blue</v>
-      </c>
-      <c r="D6" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E6" t="str">
-        <v>本次评估显示存在轻微波动，主要落在「${主要归因}」。保持现有节奏，留意变化即可。</v>
-      </c>
-      <c r="F6" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
-      </c>
-      <c r="G6" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>SELF_GROWTH_TPL_GREEN_SUMMARY</v>
-      </c>
-      <c r="B7" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C7" t="str">
-        <v>green</v>
-      </c>
-      <c r="D7" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E7" t="str">
-        <v>本次评估未发现需要重点干预的信号，当前状态整体稳定，保持现有节奏即可。</v>
-      </c>
-      <c r="F7" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
-      </c>
-      <c r="G7" t="str">
-        <v>6</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/output_template.xlsx
+++ b/business-libraries/test-data/self_growth/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL_SG_RED_1</v>
+        <v>SELF_GROWTH_TPL_PURPLE_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>self_growth</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>purple</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
@@ -439,7 +439,7 @@
         <v>评估显示，您在「${主要归因}」上的信号已经处于需要重点关注的位置。系统已暂停常规建议并生成转介工单，心理专员会与您联系。在此之前，请优先照顾好自己的基本作息。</v>
       </c>
       <c r="F2" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL_SG_ORANGE_2</v>
+        <v>SELF_GROWTH_TPL_RED_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>self_growth</v>
       </c>
       <c r="C3" t="str">
-        <v>orange</v>
+        <v>red</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
@@ -462,7 +462,7 @@
         <v>本次评估的主要归因是「${主要归因}」，同时「${次要归因}」也需要一并关注。建议本周内安排一次支持性沟通，并从推荐工具中选一项今天就能开始的动作。</v>
       </c>
       <c r="F3" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL_SG_YELLOW_3</v>
+        <v>SELF_GROWTH_TPL_ORANGE_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>self_growth</v>
       </c>
       <c r="C4" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次评估提示「${主要归因}」值得关注，尚未到需要外部介入的程度，建议先用推荐工具自主调整。</v>
+        <v>本次评估提示「${主要归因}」已进入需要主动支持的区间。重点不是再增加任务，而是先识别消耗来源、恢复可控感。</v>
       </c>
       <c r="F4" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,30 +493,76 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL_SG_DEFAULT</v>
+        <v>SELF_GROWTH_TPL_YELLOW_SUMMARY</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>green</v>
+        <v>yellow</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
+        <v>本次评估提示「${主要归因}」值得关注，尚未到需要外部介入的程度，建议先用推荐工具自主调整。</v>
+      </c>
+      <c r="F5" t="str">
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+      </c>
+      <c r="G5" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SELF_GROWTH_TPL_BLUE_SUMMARY</v>
+      </c>
+      <c r="B6" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C6" t="str">
+        <v>blue</v>
+      </c>
+      <c r="D6" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E6" t="str">
+        <v>本次评估显示存在轻微波动，主要落在「${主要归因}」。保持现有节奏，留意变化即可。</v>
+      </c>
+      <c r="F6" t="str">
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+      </c>
+      <c r="G6" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SELF_GROWTH_TPL_GREEN_SUMMARY</v>
+      </c>
+      <c r="B7" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C7" t="str">
+        <v>green</v>
+      </c>
+      <c r="D7" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E7" t="str">
         <v>本次评估未发现需要重点干预的信号，当前状态整体稳定，保持现有节奏即可。</v>
       </c>
-      <c r="F5" t="str">
-        <v>兜底模板：命中未覆盖等级时使用</v>
-      </c>
-      <c r="G5" t="str">
-        <v>99</v>
+      <c r="F7" t="str">
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+      </c>
+      <c r="G7" t="str">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/output_template.xlsx
+++ b/business-libraries/test-data/self_growth/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -482,7 +482,7 @@
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次评估提示「${主要归因}」值得关注，尚未到需要外部介入的程度，建议先用推荐工具自主调整。</v>
+        <v>本次评估提示「${主要归因}」值得关注。心理资本出现消耗，建议先用推荐工具自主调整，本周内完成至少一个微行动。</v>
       </c>
       <c r="F4" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -493,30 +493,53 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL_SG_DEFAULT</v>
+        <v>TPL_SG_BLUE_4</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>green</v>
+        <v>blue</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
+        <v>六维评估显示「${主要归因}」开始出现信号，尚未到需要外部介入的程度。建议从推荐工具中选一项今天就能开始的动作，保持观察。</v>
+      </c>
+      <c r="F5" t="str">
+        <v>可用占位符见 ⑩ 说明</v>
+      </c>
+      <c r="G5" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TPL_SG_DEFAULT</v>
+      </c>
+      <c r="B6" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C6" t="str">
+        <v>green</v>
+      </c>
+      <c r="D6" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E6" t="str">
         <v>本次评估未发现需要重点干预的信号，当前状态整体稳定，保持现有节奏即可。</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F6" t="str">
         <v>兜底模板：命中未覆盖等级时使用</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G6" t="str">
         <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>